--- a/state/daysee_grants_delta_latest.xlsx
+++ b/state/daysee_grants_delta_latest.xlsx
@@ -61,10 +61,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,11 +434,11 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
@@ -450,66 +450,66 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>run_type</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>delta_run</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
+          <t>current_count</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>current_count</t>
+          <t>previous_count</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>previous_count</t>
+          <t>new_count</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>new_count</t>
+          <t>updated_count</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>removed_count</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>updated_count</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>removed_count</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
+          <t>generated_at</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:19:17</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -526,29 +526,29 @@
   <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -661,33 +661,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="43" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -788,26 +787,21 @@
           <t>detail_url</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>changed_fields</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
+    </row>
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>原住民族委員會</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>企業｜個人</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -822,17 +816,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>婦女｜產業發展｜青年</t>
+          <t>原住民｜產業發展</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>婦女</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -840,41 +834,37 @@
           <t>產業發展</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mol.gov.tw/</t>
+          <t>https://www.cip.gov.tw/</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>www.mol.gov.tw</t>
+          <t>www.cip.gov.tw</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mol.gov.tw/</t>
+          <t>https://www.cip.gov.tw/</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>www.mol.gov.tw</t>
+          <t>www.cip.gov.tw</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -884,29 +874,24 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-446/</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | organizer_site_url | official_organizer_site_url | official_url_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
+          <t>https://dayseechat.com/subsidy/grant-439/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>115年度數位服務創新補助計畫</t>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>數位發展部</t>
+          <t>客家委員會</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -916,27 +901,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜創新創業</t>
+          <t>客家｜文化藝文</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>客家</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>創新創業</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -944,32 +929,32 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
+          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>115年度數位服務創新補助計畫</t>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://moda.gov.tw/</t>
+          <t>https://www.hakka.gov.tw/</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>moda.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://moda.gov.tw/</t>
+          <t>https://www.hakka.gov.tw/</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>moda.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -979,16 +964,11 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-448/</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | organizer_site_url | official_organizer_site_url | official_url_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
+          <t>https://dayseechat.com/subsidy/grant-437/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
@@ -1001,7 +981,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>企業 個人 民間團體</t>
+          <t>企業｜個人｜民間團體</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1077,26 +1057,21 @@
           <t>https://dayseechat.com/subsidy/grant-447/</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>數位發展部</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>企業 民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1106,22 +1081,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>婦女｜產業發展</t>
+          <t>創新創業｜產業發展</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>婦女</t>
+          <t>創新創業</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1134,64 +1109,59 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>115年度數位服務創新補助計畫</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-448/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-438/</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>客家委員會</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>學校 民間團體</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1201,27 +1171,27 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>客家｜文化藝文</t>
+          <t>婦女｜產業發展</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>客家</t>
+          <t>婦女</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -1229,32 +1199,32 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/chhakka/index</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>www.hakka.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/chhakka/index</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>www.hakka.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1264,59 +1234,54 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-437/</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
+          <t>https://dayseechat.com/subsidy/grant-438/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>原住民族委員會</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>企業 個人</t>
+          <t>個人｜其他對象｜民間團體</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜原住民</t>
+          <t>生態環境｜社區議題</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>原住民</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1324,32 +1289,32 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
+          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
+          <t>https://www.gov.taipei/</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>www.cip.gov.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
+          <t>https://www.gov.taipei/</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>www.cip.gov.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1359,19 +1324,14 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-439/</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
+          <t>https://dayseechat.com/subsidy/grant-440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1381,176 +1341,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>個人 其他對象 民間團體</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>生態環境｜社區議題</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
+          <t>原住民</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.taipei/</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-440/</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
           <t>https://dayseechat.com/subsidy/grant-441/</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
         </is>
       </c>
     </row>
@@ -1568,29 +1420,29 @@
   <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>

--- a/state/daysee_grants_delta_latest.xlsx
+++ b/state/daysee_grants_delta_latest.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25 20:19:17</t>
+          <t>2026-04-25 20:28:27</t>
         </is>
       </c>
     </row>
@@ -661,10 +661,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -677,12 +677,12 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="45" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
     <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
     <col width="43" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -791,37 +791,37 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>原住民族委員會</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>企業｜個人</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>原住民｜產業發展</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -829,578 +829,38 @@
           <t>原住民</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.cip.gov.tw/</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>www.cip.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cip.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>www.cip.gov.tw</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-439/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>客家委員會</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>客家｜文化藝文</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>客家</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hakka.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>www.hakka.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hakka.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>www.hakka.gov.tw</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-437/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>企業｜個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>產業發展｜農漁村議題</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-447/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>數位發展部</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>創新創業｜產業發展</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://moda.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>moda.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>https://moda.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>moda.gov.tw</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-448/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>勞動部</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>婦女｜產業發展</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-438/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>個人｜其他對象｜民間團體</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>台北</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>51萬-100萬</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>生態環境｜社區議題</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-440/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>bing_title_no_match</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-441/</t>
         </is>

--- a/state/daysee_grants_delta_latest.xlsx
+++ b/state/daysee_grants_delta_latest.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25 20:28:27</t>
+          <t>2026-04-25 20:57:12</t>
         </is>
       </c>
     </row>
@@ -523,29 +523,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="33" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="31" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="43" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -647,6 +647,6560 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>detail_url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-407/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>中小企業接班轉型計畫</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.value-chain.com.tw/news_info.asp?id=731</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>中小企業接班轉型計畫</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.value-chain.com.tw/news_info.asp?id=731</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>www.value-chain.com.tw</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.value-chain.com.tw/news_info.asp?id=731</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>www.value-chain.com.tw</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-353/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>中小製造業接班傳承AI應用數位轉型主題式研發計畫補助</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>中小製造業接班傳承AI應用數位轉型主題式研發計畫補助</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>keid.nat.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>keid.nat.gov.tw</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-356/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>115年親海無礙海洋創生行動方案</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>海洋委員會</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>生態環境｜社區議題</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年親海無礙海洋創生行動方案</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>115年親海無礙海洋創生行動方案</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oac.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>www.oac.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oac.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>www.oac.gov.tw</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>manual_verified_override</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-375/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>115年促轉基金還原歷史真相旗艦計畫</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>國家發展委員會</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>個人｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文｜社區議題</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年促轉基金還原歷史真相旗艦計畫</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>115年促轉基金還原歷史真相旗艦計畫</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ndc.gov.tw/nc_14813_40016</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>www.ndc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ndc.gov.tw/nc_14813_40016</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>www.ndc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>manual_verified_override</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-431/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>115年度中小微企業AI創新應用輔導計畫國際鏈結</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>創新創業｜產業發展</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度中小微企業AI創新應用輔導計畫國際鏈結</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>115年度中小微企業AI創新應用輔導計畫國際鏈結</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-427/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>115年度商業服務業機器人應用輔導計畫</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>創新創業｜產業發展</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度商業服務業機器人應用輔導計畫</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>115年度商業服務業機器人應用輔導計畫</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-416/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>115年度客家知識體系發展獎勵補助計畫</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>客家委員會</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>個人｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>客家｜文化藝文</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>客家</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度客家知識體系發展獎勵補助計畫</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>115年度客家知識體系發展獎勵補助計畫</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-411/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>115年度彰化縣地方型SBIR產業創新研發計畫</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>彰化</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>115年度彰化縣地方型SBIR產業創新研發計畫</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>www.chcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>www.chcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-361/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>115年度新北市社區營造一般性計畫</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>個人｜民間團體</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文｜社區議題</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度新北市社區營造一般性計畫</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>115年度新北市社區營造一般性計畫</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.culture.ntpc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>www.culture.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.culture.ntpc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>www.culture.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>manual_verified_override</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-414/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>115年度新竹縣社區營造計畫提案補助</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>個人｜民間團體</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>新竹</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下｜11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文｜社區議題</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度新竹縣社區營造計畫提案補助</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>115年度新竹縣社區營造計畫提案補助</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hsinchu.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>www.hsinchu.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hsinchu.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>www.hsinchu.gov.tw</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-436/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>115年度第2期臺北市觀光活動補助</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度第2期臺北市觀光活動補助</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>115年度第2期臺北市觀光活動補助</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>www.gov.taipei</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>www.gov.taipei</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-393/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>115年度第2期臺北市電影製作補助</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文｜產業發展</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度第2期臺北市電影製作補助</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>115年度第2期臺北市電影製作補助</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>www.gov.taipei</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>www.gov.taipei</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>115年推動社區運動俱樂部實施計畫</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>企業｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年推動社區運動俱樂部實施計畫</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>115年推動社區運動俱樂部實施計畫</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edu.tw/</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>www.edu.tw</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edu.tw/</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>www.edu.tw</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-418/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>115年教育優先區中小學暑假營隊活動補助</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>孩童｜青年</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>孩童</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年教育優先區中小學暑假營隊活動補助</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>115年教育優先區中小學暑假營隊活動補助</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edu.tw/</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>www.edu.tw</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edu.tw/</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>www.edu.tw</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-425/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>115年智慧養殖創新事業補助計畫</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>企業｜個人｜民間團體</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>雲林</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬｜51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜農漁村議題</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年智慧養殖創新事業補助計畫</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>115年智慧養殖創新事業補助計畫</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年智慧養殖創新事業補助計畫</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>bing_title_no_match</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-432/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>115年桃園市智慧科技農業專案補助計畫</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>個人｜民間團體</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>桃園</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬｜51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜農漁村議題</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>115年桃園市智慧科技農業專案補助計畫</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>www.guishan.tycg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>www.guishan.tycg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-345/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>115年臺南青年公共參與行動計畫</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>個人｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>創新創業｜文化藝文｜生態環境｜社區議題｜青年</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>115年臺南青年公共參與行動計畫</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>bing_title_no_match</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-402/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>115年高照顧負荷家庭創新服務方案補助計畫</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>基隆</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>身心障礙</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>身心障礙</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年高照顧負荷家庭創新服務方案補助計畫</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>115年高照顧負荷家庭創新服務方案補助計畫</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年高照顧負荷家庭創新服務方案補助計畫</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>bing_title_no_match</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-443/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>親愛文化攜手計畫</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>南投</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>https://cacf.easy.co/pages/support</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>親愛文化攜手計畫</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://cacf.easy.co/pages/support</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>cacf.easy.co</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>https://cacf.easy.co/pages/support</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>cacf.easy.co</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-336/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>雙百萬運動漫畫徵選</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>文化部</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>企業｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文｜產業發展</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>雙百萬運動漫畫徵選</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>grants.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>grants.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-344/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>115年創新米糧產品量產暨市場拓銷計畫</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>農業部</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜農漁村議題</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年創新米糧產品量產暨市場拓銷計畫</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>115年創新米糧產品量產暨市場拓銷計畫</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moa.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>www.moa.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moa.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>www.moa.gov.tw</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-421/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>115年度彰化縣城鄉發展建設基金補助</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>彰化</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度彰化縣城鄉發展建設基金補助</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>115年度彰化縣城鄉發展建設基金補助</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>www.chcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>www.chcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-426/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>115年度精神復健機構改善公共安全設施設備補助計畫</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>衛生福利部</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>身心障礙</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>身心障礙</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度精神復健機構改善公共安全設施設備補助計畫</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>115年度精神復健機構改善公共安全設施設備補助計畫</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mohw.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>www.mohw.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mohw.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>www.mohw.gov.tw</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-434/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>文化部</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115至117年傳統藝術接班人外台劇藝提升計畫</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>www.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>www.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>115年度紀錄片製作補助要點</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>文化部</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文｜產業發展</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度紀錄片製作補助要點</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>115年度紀錄片製作補助要點</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>www.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>www.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-423/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>115年文化部社造築夢培養皿徵選獎勵計畫</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>文化部</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>個人</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下｜11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>115年文化部社造築夢培養皿徵選獎勵計畫</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>www.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>www.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-387/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>115年度數位服務創新補助計畫</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>數位發展部</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>創新創業｜產業發展</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>115年度數位服務創新補助計畫</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-429/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>115學年度精進童軍教育發展實施計畫</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>學校</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>孩童｜青年</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>孩童</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115學年度精進童軍教育發展實施計畫</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>115學年度精進童軍教育發展實施計畫</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edu.tw/</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>www.edu.tw</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edu.tw/</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>www.edu.tw</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-444/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>115年下半年度藝文及民俗節慶活動補助</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文｜社區議題</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年下半年度藝文及民俗節慶活動補助</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>115年下半年度藝文及民俗節慶活動補助</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年下半年度藝文及民俗節慶活動補助</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>bing_title_no_match</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-445/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>基隆市青年參與公益活動補助計畫</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>基隆</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>基隆市青年參與公益活動補助計畫</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>dsa.dyhu.edu.tw</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>dsa.dyhu.edu.tw</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-389/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>企業｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬｜51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>高齡</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>高齡</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>wlb.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>wlb.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-368/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>企業｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜社區議題</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>115年度經濟部中小企業創新研發AI轉型補助計畫</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>創新創業｜產業發展</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度經濟部中小企業創新研發AI轉型補助計畫</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>115年度經濟部中小企業創新研發AI轉型補助計畫</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-395/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>桃園</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>tyoem.tycg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>tyoem.tycg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-351/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>115年文化部青年村落文化行動計畫</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>文化部</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>個人｜民間團體</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年文化部青年村落文化行動計畫</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>115年文化部青年村落文化行動計畫</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>www.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>www.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-394/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>客家影像畢業製作孵育計畫徵選</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>客家委員會</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>學校</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬｜51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>客家｜文化藝文</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>客家</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>客家影像畢業製作孵育計畫徵選</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-294/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>115年度不孕症試管嬰兒補助3.0方案</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>衛生福利部</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>個人</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上｜10萬以下｜11萬-50萬｜51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>孩童</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>孩童</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度不孕症試管嬰兒補助3.0方案</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>115年度不孕症試管嬰兒補助3.0方案</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mohw.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>www.mohw.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mohw.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>www.mohw.gov.tw</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-401/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>115年度台中市都市更新整建維護補助計畫</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/3234351/post</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>115年度台中市都市更新整建維護補助計畫</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/3234351/post</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/3234351/post</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>115年度台中拍獎勵電影事業計畫</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文｜產業發展</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度台中拍獎勵電影事業計畫</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>115年度台中拍獎勵電影事業計畫</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度台中拍獎勵電影事業計畫</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>bing_title_no_match</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-417/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>115年度臺北市住宅社區創能儲能及節能補助計畫</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>個人｜民間團體</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬｜51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>生態環境｜社區議題</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>115年度臺北市住宅社區創能儲能及節能補助計畫</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>www.gov.taipei</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>www.gov.taipei</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-371/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.twtainan.net/</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.twtainan.net/</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>www.twtainan.net</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.twtainan.net/</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>www.twtainan.net</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-385/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026新竹市政府青年AI數位工具補助</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>個人</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>新竹</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=2026新竹市政府青年AI數位工具補助</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>2026新竹市政府青年AI數位工具補助</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>https://youthhsinchu.hccg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>youthhsinchu.hccg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>https://youthhsinchu.hccg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>youthhsinchu.hccg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>manual_verified_override</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-399/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動社區發展及互助共好補助計畫</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>孩童｜社區議題｜高齡</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>孩童</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>高齡</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推動社區發展及互助共好補助計畫</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動社區發展及互助共好補助計畫</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推動社區發展及互助共好補助計畫</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>bing_title_no_match</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-408/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動資源循環地方創生計畫</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>環境部</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>生態環境｜產業發展｜社區議題</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推動資源循環地方創生計畫</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動資源循環地方創生計畫</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moenv.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>www.moenv.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moenv.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>www.moenv.gov.tw</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-412/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>基隆</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>社區議題｜身心障礙</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>身心障礙</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-433/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>高雄市政府會議展覽活動擴大補助計畫</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>企業｜其他對象｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>高雄</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文｜產業發展</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=高雄市政府會議展覽活動擴大補助計畫</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>高雄市政府會議展覽活動擴大補助計畫</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>www.kcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>www.kcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-435/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>115年度A+企業創新研發淬錬次世代通訊計畫</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>創新創業｜產業發展</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度A%2B企業創新研發淬錬次世代通訊計畫</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>115年度A+企業創新研發淬錬次世代通訊計畫</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-442/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>www.economic.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>www.economic.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>manual_verified_override</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-410/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>www.economic.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>www.economic.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>manual_verified_override</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-420/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>115年度新北市低碳社區改造補助</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>其他對象</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下｜11萬-50萬｜51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>生態環境｜社區議題</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>115年度新北市低碳社區改造補助</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>www.epd.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>www.epd.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-378/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>115年度補助文化活動作業</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>個人｜民間團體</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>基隆</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>115年度補助文化活動作業</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>klctb.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>klctb.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-314/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>衛生福利部</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>個人</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>婦女｜孩童｜身心障礙</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>孩童</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>身心障礙</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=%E8%A1%9B%E7%94%9F%E7%A6%8F%E5%88%A9%E9%83%A8%E7%A4%BE%E6%9C%83%E5%8F%8A%E5%AE%B6%E5%BA%AD%E7%BD%B2114%E5%B9%B4%E5%96%AE%E8%A6%AA%E6%89%B6%E5%8A%A9%E8%A8%88%E7%95%AB</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mohw.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>www.mohw.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mohw.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>www.mohw.gov.tw</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-246/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>115年臺南地方產業原鄉永續小旅行振興計畫</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>生態環境｜產業發展</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>115年臺南地方產業原鄉永續小旅行振興計畫</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>bing_title_no_match</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-391/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>115年度AI工具庫點數補助計畫</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>創新創業｜產業發展</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度AI工具庫點數補助計畫</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>115年度AI工具庫點數補助計畫</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>115年度台中市公寓大廈成立管委會獎勵補助計畫</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>115年度台中市公寓大廈成立管委會獎勵補助計畫</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>thd.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>thd.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-370/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>115年度台中市公寓大廈成立管理委員會補助</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>其他對象｜民間團體</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度台中市公寓大廈成立管理委員會補助</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>115年度台中市公寓大廈成立管理委員會補助</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-390/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動事業單位辦理職前培訓計畫</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>企業｜學校</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜青年</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動事業單位辦理職前培訓計畫</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>tcnr.wda.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>tcnr.wda.gov.tw</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-334/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>115年臺南市民旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺南市民旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>115年臺南市民旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tainan.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>www.tainan.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tainan.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>www.tainan.gov.tw</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-392/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>115年品牌臺東產業行銷補助</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>台東</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下｜11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>115年品牌臺東產業行銷補助</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>bdsone.taitung.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>bdsone.taitung.gov.tw</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-284/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>115年度高雄市觀光行銷推廣補助計畫</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>高雄</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下｜11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>115年度高雄市觀光行銷推廣補助計畫</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>khh.travel</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>khh.travel</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-327/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>115年臺南市家戶屋頂設置太陽光電加速計畫</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>個人</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上｜10萬以下</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115%E5%B9%B4%E8%87%BA%E5%8D%97%E5%B8%82%E5%AE%B6%E6%88%B6%E5%B1%8B%E9%A0%82%E8%A8%AD%E7%BD%AE%E5%A4%AA%E9%99%BD%E5%85%89%E9%9B%BB%E5%8A%A0%E9%80%9F%E8%A8%88%E7%95%AB</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>115年臺南市家戶屋頂設置太陽光電加速計畫</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tainan.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>www.tainan.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tainan.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>www.tainan.gov.tw</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-380/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>115年度高雄市公寓大廈共用部分維護修繕費用補助</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>其他對象</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>高雄</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115%E5%B9%B4%E5%BA%A6%E9%AB%98%E9%9B%84%E5%B8%82%E5%85%AC%E5%AF%93%E5%A4%A7%E5%BB%88%E5%85%B1%E7%94%A8%E9%83%A8%E5%88%86%E7%B6%AD%E8%AD%B7%E4%BF%AE%E7%B9%95%E8%B2%BB%E7%94%A8%E8%A3%9C%E5%8A%A9</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>115年度高雄市公寓大廈共用部分維護修繕費用補助</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>www.kcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>www.kcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-381/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>115年度彰化縣社區發展協會一般性補助</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>彰化</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度彰化縣社區發展協會一般性補助</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>115年度彰化縣社區發展協會一般性補助</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>www.chcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>www.chcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-419/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>115年度彰化縣社區發展協會一般性補助</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>彰化</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度彰化縣社區發展協會一般性補助</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>115年度彰化縣社區發展協會一般性補助</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>www.chcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>www.chcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-424/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>基隆</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>生態環境｜產業發展</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-415/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>全國性運動團體辦理全民運動相關活動計畫</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>全國性運動團體辦理全民運動相關活動計畫</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>isports.sa.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>isports.sa.gov.tw</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-300/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>115年度小型企業創新研發計畫SBIR</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>https://sbir.org.tw/</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>115年度小型企業創新研發計畫SBIR</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>https://sbir.org.tw/</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>sbir.org.tw</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>https://sbir.org.tw/</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>sbir.org.tw</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-365/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>115年度臺北市產業發展獎勵補助計畫SITI</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.industry-incentive.taipei/</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>115年度臺北市產業發展獎勵補助計畫SITI</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.industry-incentive.taipei/</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>www.industry-incentive.taipei</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.industry-incentive.taipei/</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>www.industry-incentive.taipei</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-363/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>115年海洋保育國際交流活動獎助計畫</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>海洋委員會</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>個人｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下｜11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>115年海洋保育國際交流活動獎助計畫</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>www.oca.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>www.oca.gov.tw</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-319/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>孩童｜社區議題</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>孩童</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sw.ntpc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>www.sw.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sw.ntpc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>www.sw.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>manual_verified_override</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-428/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>商業服務業AI解決方案補助計畫</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>商業服務業AI解決方案補助計畫</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>www.smebiz.org.tw</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>www.smebiz.org.tw</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>基隆</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上｜10萬以下</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>社區議題｜高齡</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>高齡</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-331/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027高雄馬祖團體旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>連江｜高雄</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>2026高雄馬祖團體旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>bing_title_no_match</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-383/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>商業服務業AI解決方案補助計畫</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>商業服務業AI解決方案補助計畫</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>www.smebiz.org.tw</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>www.smebiz.org.tw</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-349/</t>
         </is>
       </c>
     </row>

--- a/state/daysee_grants_delta_latest.xlsx
+++ b/state/daysee_grants_delta_latest.xlsx
@@ -431,85 +431,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>metric</t>
+          <t>current_count</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>previous_count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>new_count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>updated_count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>removed_count</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>current_count</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>83</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>previous_count</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="C2" s="2" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>new_count</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>updated_count</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>removed_count</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
+      <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>generated_at</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:57:12</t>
-        </is>
+      <c r="E2" s="2" t="n">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -523,7 +496,831 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T76"/>
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="25" customWidth="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>detail_url</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>plan_source</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>eligible_targets</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>applicable_region</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>grant_amount</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>deadline_date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>deadline_text</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>topic_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>topic_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>topic_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>topic_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>topic_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>organizer_site_url</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>organizer_site_domain</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>official_organizer_site_url</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>official_organizer_domain</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>official_url_status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>official_url_confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-446/</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>不分金額｜115年度推動工作與生活平衡補助計畫｜＃關注議題：｜婦女｜產業發展｜＃補助對象：｜企業｜民間團體｜＃計畫來源：｜勞動部｜＃補助金額：｜72</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>115年度數位服務創新補助計畫</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-448/</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>數位發展部</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上｜115年度A+企業創新研發淬錬次世代通訊計畫｜＃關注議題：｜創新創業｜產業發展｜＃補助對象：｜企業｜民間團體｜＃計畫來源：｜經濟部｜＃補助金額：｜33</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>https://im666.tw/digital-service-innovation-subsidy-program</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>im666.tw</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>search_verified_non_gov</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-447/</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>企業｜個人｜民間團體</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>不分金額｜115年度推動工作與生活平衡補助計畫｜＃關注議題：｜婦女｜產業發展｜青年｜＃補助對象：｜企業｜＃計畫來源：｜勞動部｜＃補助金額：｜40</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>search_no_match</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-438/</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>不分金額｜115年度推動工作與生活平衡補助計畫｜＃關注議題：｜婦女｜產業發展｜青年｜＃補助對象：｜企業｜＃計畫來源：｜勞動部｜＃補助金額：｜40</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>search_no_match</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-437/</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>客家委員會</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>不分金額｜115年度客家知識體系發展獎勵補助計畫｜＃關注議題：｜客家｜文化藝文｜＃補助對象：｜個人｜學校｜民間團體｜＃計畫來源：｜客家委員會｜＃補助金額：｜50</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>客家</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>search_no_match</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>115年度原住民族促進就業獎勵計畫</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-439/</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>原住民族委員會</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>企業｜個人</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下｜115年度補助原住民參加國家考試實施計畫｜＃關注議題：｜原住民｜＃補助對象：｜個人｜＃計畫來源：｜縣市政府｜＃補助金額：｜24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>原住民</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>search_no_match</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-440/</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>個人｜其他對象｜民間團體</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上｜115年度推動資源循環地方創生計畫｜＃關注議題：｜生態環境｜產業發展｜社區議題｜＃補助對象：｜企業｜民間團體｜＃計畫來源：｜環境部｜＃補助金額：｜118</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>search_no_match</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-441/</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>個人</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。｜必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。｜計畫撰寫技巧｜確認發票規定｜務必確保發票為當年度開立，且日期必須在考試日期之前。｜到考證明清晰｜准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。｜補習班須合法｜報名前請先確認該補習機構為臺中市合法立案，以免不符資格。｜及早提出申請｜因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。｜文件準備齊全｜送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。｜返回主頁｜你可能也會喜歡這些資訊...｜不分金額｜115年度原住民族促進就業獎勵計畫｜＃關注議題：｜原住民｜產業發展｜＃補助對象：｜企業｜個人｜＃計畫來源：｜原住民族委員會｜＃補助金額：｜48</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>原住民</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>search_no_match</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>detail_url</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>plan_source</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>eligible_targets</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>applicable_region</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>grant_amount</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>deadline_date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>deadline_text</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>topic_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>topic_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>topic_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>topic_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>topic_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>organizer_site_url</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>organizer_site_domain</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>official_organizer_site_url</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>official_organizer_domain</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>official_url_status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>official_url_confidence</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1181,17 +1978,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>115年度商業服務業機器人應用輔導計畫</t>
+          <t>115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>原住民族委員會</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>企業｜個人</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1211,12 +2008,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>創新創業｜產業發展</t>
+          <t>原住民｜產業發展</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>創新創業</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1229,32 +2026,32 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度商業服務業機器人應用輔導計畫</t>
+          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>115年度商業服務業機器人應用輔導計畫</t>
+          <t>115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.moea.gov.tw/</t>
+          <t>https://www.cip.gov.tw/</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>www.moea.gov.tw</t>
+          <t>www.cip.gov.tw</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>https://www.moea.gov.tw/</t>
+          <t>https://www.cip.gov.tw/</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>www.moea.gov.tw</t>
+          <t>www.cip.gov.tw</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1264,24 +2061,24 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-416/</t>
+          <t>https://dayseechat.com/subsidy/grant-439/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>115年度客家知識體系發展獎勵補助計畫</t>
+          <t>115年度商業服務業機器人應用輔導計畫</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>客家委員會</t>
+          <t>經濟部</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>個人｜學校｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1301,17 +2098,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>客家｜文化藝文</t>
+          <t>創新創業｜產業發展</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>客家</t>
+          <t>創新創業</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -1319,32 +2116,32 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度客家知識體系發展獎勵補助計畫</t>
+          <t>https://www.google.com/search?q=115年度商業服務業機器人應用輔導計畫</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>115年度客家知識體系發展獎勵補助計畫</t>
+          <t>115年度商業服務業機器人應用輔導計畫</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/</t>
+          <t>https://www.moea.gov.tw/</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>www.hakka.gov.tw</t>
+          <t>www.moea.gov.tw</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/</t>
+          <t>https://www.moea.gov.tw/</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>www.hakka.gov.tw</t>
+          <t>www.moea.gov.tw</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1354,34 +2151,34 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-411/</t>
+          <t>https://dayseechat.com/subsidy/grant-416/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>115年度彰化縣地方型SBIR產業創新研發計畫</t>
+          <t>115年度客家知識體系發展獎勵補助計畫</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>客家委員會</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>個人｜學校｜民間團體</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>彰化</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1391,63 +2188,67 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>客家｜文化藝文</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t>客家</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
+          <t>https://www.google.com/search?q=115年度客家知識體系發展獎勵補助計畫</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>115年度彰化縣地方型SBIR產業創新研發計畫</t>
+          <t>115年度客家知識體系發展獎勵補助計畫</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
+          <t>https://www.hakka.gov.tw/</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>www.chcg.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
+          <t>https://www.hakka.gov.tw/</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>www.chcg.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-361/</t>
+          <t>https://dayseechat.com/subsidy/grant-411/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>115年度新北市社區營造一般性計畫</t>
+          <t>115年度彰化縣地方型SBIR產業創新研發計畫</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1457,17 +2258,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>個人｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>新北</t>
+          <t>彰化</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1477,87 +2278,83 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>文化藝文｜社區議題</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度新北市社區營造一般性計畫</t>
+          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>115年度新北市社區營造一般性計畫</t>
+          <t>115年度彰化縣地方型SBIR產業創新研發計畫</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.culture.ntpc.gov.tw/</t>
+          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>www.culture.ntpc.gov.tw</t>
+          <t>www.chcg.gov.tw</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>https://www.culture.ntpc.gov.tw/</t>
+          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>www.culture.ntpc.gov.tw</t>
+          <t>www.chcg.gov.tw</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>manual_verified_override</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-414/</t>
+          <t>https://dayseechat.com/subsidy/grant-361/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>115年度新竹縣社區營造計畫提案補助</t>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>客家委員會</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>個人｜民間團體</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>新竹</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10萬以下｜11萬-50萬</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1567,17 +2364,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>文化藝文｜社區議題</t>
+          <t>客家｜文化藝文</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>客家</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1585,32 +2382,32 @@
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度新竹縣社區營造計畫提案補助</t>
+          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>115年度新竹縣社區營造計畫提案補助</t>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.hsinchu.gov.tw/</t>
+          <t>https://www.hakka.gov.tw/</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>www.hsinchu.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>https://www.hsinchu.gov.tw/</t>
+          <t>https://www.hakka.gov.tw/</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>www.hsinchu.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1620,14 +2417,14 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-436/</t>
+          <t>https://dayseechat.com/subsidy/grant-437/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>115年度第2期臺北市觀光活動補助</t>
+          <t>115年度新北市社區營造一般性計畫</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1637,12 +2434,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>個人｜民間團體</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>新北</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1657,63 +2454,67 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>文化藝文｜社區議題</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度第2期臺北市觀光活動補助</t>
+          <t>https://www.google.com/search?q=115年度新北市社區營造一般性計畫</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>115年度第2期臺北市觀光活動補助</t>
+          <t>115年度新北市社區營造一般性計畫</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.taipei/</t>
+          <t>https://www.culture.ntpc.gov.tw/</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>www.gov.taipei</t>
+          <t>www.culture.ntpc.gov.tw</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.taipei/</t>
+          <t>https://www.culture.ntpc.gov.tw/</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>www.gov.taipei</t>
+          <t>www.culture.ntpc.gov.tw</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>manual_verified_override</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-393/</t>
+          <t>https://dayseechat.com/subsidy/grant-414/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>115年度第2期臺北市電影製作補助</t>
+          <t>115年度新竹縣社區營造計畫提案補助</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1723,17 +2524,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>個人｜民間團體</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>新竹</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1743,7 +2544,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>文化藝文｜產業發展</t>
+          <t>文化藝文｜社區議題</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1753,7 +2554,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1761,32 +2562,32 @@
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度第2期臺北市電影製作補助</t>
+          <t>https://www.google.com/search?q=115年度新竹縣社區營造計畫提案補助</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>115年度第2期臺北市電影製作補助</t>
+          <t>115年度新竹縣社區營造計畫提案補助</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.taipei/</t>
+          <t>https://www.hsinchu.gov.tw/</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>www.gov.taipei</t>
+          <t>www.hsinchu.gov.tw</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.taipei/</t>
+          <t>https://www.hsinchu.gov.tw/</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>www.gov.taipei</t>
+          <t>www.hsinchu.gov.tw</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1796,29 +2597,29 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-405/</t>
+          <t>https://dayseechat.com/subsidy/grant-436/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>115年推動社區運動俱樂部實施計畫</t>
+          <t>115年度第2期臺北市觀光活動補助</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>企業｜學校｜民間團體</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1833,12 +2634,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1847,32 +2648,32 @@
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年推動社區運動俱樂部實施計畫</t>
+          <t>https://www.google.com/search?q=115年度第2期臺北市觀光活動補助</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>115年推動社區運動俱樂部實施計畫</t>
+          <t>115年度第2期臺北市觀光活動補助</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.edu.tw/</t>
+          <t>https://www.gov.taipei/</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>www.edu.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>https://www.edu.tw/</t>
+          <t>https://www.gov.taipei/</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>www.edu.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -1882,34 +2683,34 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-418/</t>
+          <t>https://dayseechat.com/subsidy/grant-393/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>115年教育優先區中小學暑假營隊活動補助</t>
+          <t>115年度第2期臺北市電影製作補助</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>學校｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1919,17 +2720,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>孩童｜青年</t>
+          <t>文化藝文｜產業發展</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>孩童</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1937,32 +2738,32 @@
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年教育優先區中小學暑假營隊活動補助</t>
+          <t>https://www.google.com/search?q=115年度第2期臺北市電影製作補助</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>115年教育優先區中小學暑假營隊活動補助</t>
+          <t>115年度第2期臺北市電影製作補助</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.edu.tw/</t>
+          <t>https://www.gov.taipei/</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>www.edu.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>https://www.edu.tw/</t>
+          <t>https://www.gov.taipei/</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>www.edu.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -1972,34 +2773,34 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-425/</t>
+          <t>https://dayseechat.com/subsidy/grant-405/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>115年智慧養殖創新事業補助計畫</t>
+          <t>115年推動社區運動俱樂部實施計畫</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>教育部</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>企業｜個人｜民間團體</t>
+          <t>企業｜學校｜民間團體</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>雲林</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬｜51萬-100萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2009,79 +2810,83 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜農漁村議題</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年智慧養殖創新事業補助計畫</t>
+          <t>https://www.google.com/search?q=115年推動社區運動俱樂部實施計畫</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>115年智慧養殖創新事業補助計畫</t>
+          <t>115年推動社區運動俱樂部實施計畫</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年智慧養殖創新事業補助計畫</t>
+          <t>https://www.edu.tw/</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
+          <t>www.edu.tw</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edu.tw/</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>www.edu.tw</t>
+        </is>
+      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-432/</t>
+          <t>https://dayseechat.com/subsidy/grant-418/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>115年桃園市智慧科技農業專案補助計畫</t>
+          <t>115年教育優先區中小學暑假營隊活動補助</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>教育部</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>個人｜民間團體</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>桃園</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬｜51萬-100萬</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2091,17 +2896,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜農漁村議題</t>
+          <t>孩童｜青年</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>孩童</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>農漁村議題</t>
+          <t>青年</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -2109,49 +2914,49 @@
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
+          <t>https://www.google.com/search?q=115年教育優先區中小學暑假營隊活動補助</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>115年桃園市智慧科技農業專案補助計畫</t>
+          <t>115年教育優先區中小學暑假營隊活動補助</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
+          <t>https://www.edu.tw/</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>www.guishan.tycg.gov.tw</t>
+          <t>www.edu.tw</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
+          <t>https://www.edu.tw/</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>www.guishan.tycg.gov.tw</t>
+          <t>www.edu.tw</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-345/</t>
+          <t>https://dayseechat.com/subsidy/grant-425/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>115年臺南青年公共參與行動計畫</t>
+          <t>115年智慧養殖創新事業補助計畫</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2161,17 +2966,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>個人｜學校｜民間團體</t>
+          <t>企業｜個人｜民間團體</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>雲林</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2181,47 +2986,35 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>創新創業｜文化藝文｜生態環境｜社區議題｜青年</t>
+          <t>產業發展｜農漁村議題</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>創新創業</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
+          <t>農漁村議題</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
+          <t>https://www.google.com/search?q=115年智慧養殖創新事業補助計畫</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>115年臺南青年公共參與行動計畫</t>
+          <t>115年智慧養殖創新事業補助計畫</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
+          <t>https://www.google.com/search?q=115年智慧養殖創新事業補助計畫</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2238,14 +3031,14 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-402/</t>
+          <t>https://dayseechat.com/subsidy/grant-432/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>115年高照顧負荷家庭創新服務方案補助計畫</t>
+          <t>115年桃園市智慧科技農業專案補助計畫</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2255,17 +3048,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>企業｜民間團體</t>
+          <t>個人｜民間團體</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>基隆</t>
+          <t>桃園</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2275,55 +3068,67 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>身心障礙</t>
+          <t>產業發展｜農漁村議題</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>身心障礙</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年高照顧負荷家庭創新服務方案補助計畫</t>
+          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>115年高照顧負荷家庭創新服務方案補助計畫</t>
+          <t>115年桃園市智慧科技農業專案補助計畫</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年高照顧負荷家庭創新服務方案補助計畫</t>
+          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
+          <t>www.guishan.tycg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>www.guishan.tycg.gov.tw</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-443/</t>
+          <t>https://dayseechat.com/subsidy/grant-345/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>親愛文化攜手計畫</t>
+          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2333,17 +3138,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>學校｜民間團體</t>
+          <t>企業｜個人｜民間團體</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>南投</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2353,83 +3158,87 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>產業發展｜農漁村議題</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>https://cacf.easy.co/pages/support</t>
+          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>親愛文化攜手計畫</t>
+          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>https://cacf.easy.co/pages/support</t>
+          <t>https://www.taichung.gov.tw/</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>cacf.easy.co</t>
+          <t>www.taichung.gov.tw</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>https://cacf.easy.co/pages/support</t>
+          <t>https://www.taichung.gov.tw/</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>cacf.easy.co</t>
+          <t>www.taichung.gov.tw</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-336/</t>
+          <t>https://dayseechat.com/subsidy/grant-447/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>雙百萬運動漫畫徵選</t>
+          <t>115年臺南青年公共參與行動計畫</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>企業｜學校｜民間團體</t>
+          <t>個人｜學校｜民間團體</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2439,157 +3248,149 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>文化藝文｜產業發展</t>
+          <t>創新創業｜文化藝文｜生態環境｜社區議題｜青年</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
           <t>文化藝文</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
+          <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>雙百萬運動漫畫徵選</t>
+          <t>115年臺南青年公共參與行動計畫</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
+          <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>grants.moc.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>grants.moc.gov.tw</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-344/</t>
+          <t>https://dayseechat.com/subsidy/grant-402/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>115年創新米糧產品量產暨市場拓銷計畫</t>
+          <t>115年高照顧負荷家庭創新服務方案補助計畫</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>農業部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>基隆</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜農漁村議題</t>
+          <t>身心障礙</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
+          <t>身心障礙</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年創新米糧產品量產暨市場拓銷計畫</t>
+          <t>https://www.google.com/search?q=115年高照顧負荷家庭創新服務方案補助計畫</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>115年創新米糧產品量產暨市場拓銷計畫</t>
+          <t>115年高照顧負荷家庭創新服務方案補助計畫</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>https://www.moa.gov.tw/</t>
+          <t>https://www.google.com/search?q=115年高照顧負荷家庭創新服務方案補助計畫</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>www.moa.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.moa.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>www.moa.gov.tw</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-421/</t>
+          <t>https://dayseechat.com/subsidy/grant-443/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>115年度彰化縣城鄉發展建設基金補助</t>
+          <t>親愛文化攜手計畫</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2599,32 +3400,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>彰化</t>
+          <t>南投</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -2633,59 +3434,59 @@
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度彰化縣城鄉發展建設基金補助</t>
+          <t>https://cacf.easy.co/pages/support</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>115年度彰化縣城鄉發展建設基金補助</t>
+          <t>親愛文化攜手計畫</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>https://www.chcg.gov.tw/</t>
+          <t>https://cacf.easy.co/pages/support</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>www.chcg.gov.tw</t>
+          <t>cacf.easy.co</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>https://www.chcg.gov.tw/</t>
+          <t>https://cacf.easy.co/pages/support</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>www.chcg.gov.tw</t>
+          <t>cacf.easy.co</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-426/</t>
+          <t>https://dayseechat.com/subsidy/grant-336/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>115年度精神復健機構改善公共安全設施設備補助計畫</t>
+          <t>雙百萬運動漫畫徵選</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>衛生福利部</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>企業｜民間團體</t>
+          <t>企業｜學校｜民間團體</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2695,83 +3496,87 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>身心障礙</t>
+          <t>文化藝文｜產業發展</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>身心障礙</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度精神復健機構改善公共安全設施設備補助計畫</t>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>115年度精神復健機構改善公共安全設施設備補助計畫</t>
+          <t>雙百萬運動漫畫徵選</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>https://www.mohw.gov.tw/</t>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>www.mohw.gov.tw</t>
+          <t>grants.moc.gov.tw</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>https://www.mohw.gov.tw/</t>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>www.mohw.gov.tw</t>
+          <t>grants.moc.gov.tw</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-434/</t>
+          <t>https://dayseechat.com/subsidy/grant-344/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
+          <t>115年創新米糧產品量產暨市場拓銷計畫</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>農業部</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2781,56 +3586,60 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>產業發展｜農漁村議題</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115至117年傳統藝術接班人外台劇藝提升計畫</t>
+          <t>https://www.google.com/search?q=115年創新米糧產品量產暨市場拓銷計畫</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
+          <t>115年創新米糧產品量產暨市場拓銷計畫</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/</t>
+          <t>https://www.moa.gov.tw/</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>www.moc.gov.tw</t>
+          <t>www.moa.gov.tw</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/</t>
+          <t>https://www.moa.gov.tw/</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>www.moc.gov.tw</t>
+          <t>www.moa.gov.tw</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -2840,29 +3649,29 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-406/</t>
+          <t>https://dayseechat.com/subsidy/grant-421/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>115年度紀錄片製作補助要點</t>
+          <t>115年度彰化縣城鄉發展建設基金補助</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>企業｜民間團體</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>彰化</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2872,55 +3681,51 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>文化藝文｜產業發展</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度紀錄片製作補助要點</t>
+          <t>https://www.google.com/search?q=115年度彰化縣城鄉發展建設基金補助</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>115年度紀錄片製作補助要點</t>
+          <t>115年度彰化縣城鄉發展建設基金補助</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/</t>
+          <t>https://www.chcg.gov.tw/</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>www.moc.gov.tw</t>
+          <t>www.chcg.gov.tw</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/</t>
+          <t>https://www.chcg.gov.tw/</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>www.moc.gov.tw</t>
+          <t>www.chcg.gov.tw</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -2930,24 +3735,24 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-423/</t>
+          <t>https://dayseechat.com/subsidy/grant-426/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>115年文化部社造築夢培養皿徵選獎勵計畫</t>
+          <t>115年度精神復健機構改善公共安全設施設備補助計畫</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>衛生福利部</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>個人</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2957,22 +3762,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10萬以下｜11萬-50萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>身心障礙</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>身心障礙</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2981,59 +3786,59 @@
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
+          <t>https://www.google.com/search?q=115年度精神復健機構改善公共安全設施設備補助計畫</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>115年文化部社造築夢培養皿徵選獎勵計畫</t>
+          <t>115年度精神復健機構改善公共安全設施設備補助計畫</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
+          <t>https://www.mohw.gov.tw/</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>www.moc.gov.tw</t>
+          <t>www.mohw.gov.tw</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
+          <t>https://www.mohw.gov.tw/</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>www.moc.gov.tw</t>
+          <t>www.mohw.gov.tw</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-387/</t>
+          <t>https://dayseechat.com/subsidy/grant-434/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>115年度數位服務創新補助計畫</t>
+          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>數位發展部</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3048,55 +3853,51 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>創新創業｜產業發展</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
+          <t>https://www.google.com/search?q=115至117年傳統藝術接班人外台劇藝提升計畫</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>115年度數位服務創新補助計畫</t>
+          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>https://moda.gov.tw/</t>
+          <t>https://www.moc.gov.tw/</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>moda.gov.tw</t>
+          <t>www.moc.gov.tw</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>https://moda.gov.tw/</t>
+          <t>https://www.moc.gov.tw/</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>moda.gov.tw</t>
+          <t>www.moc.gov.tw</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3106,24 +3907,24 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-429/</t>
+          <t>https://dayseechat.com/subsidy/grant-406/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>115學年度精進童軍教育發展實施計畫</t>
+          <t>115年度紀錄片製作補助要點</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>學校</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3133,27 +3934,27 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>孩童｜青年</t>
+          <t>文化藝文｜產業發展</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>孩童</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -3161,32 +3962,32 @@
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115學年度精進童軍教育發展實施計畫</t>
+          <t>https://www.google.com/search?q=115年度紀錄片製作補助要點</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>115學年度精進童軍教育發展實施計畫</t>
+          <t>115年度紀錄片製作補助要點</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>https://www.edu.tw/</t>
+          <t>https://www.moc.gov.tw/</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>www.edu.tw</t>
+          <t>www.moc.gov.tw</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>https://www.edu.tw/</t>
+          <t>https://www.moc.gov.tw/</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>www.edu.tw</t>
+          <t>www.moc.gov.tw</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3196,192 +3997,200 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-444/</t>
+          <t>https://dayseechat.com/subsidy/grant-423/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>115年下半年度藝文及民俗節慶活動補助</t>
+          <t>115年文化部社造築夢培養皿徵選獎勵計畫</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>學校｜民間團體</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>台中</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>文化藝文｜社區議題</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
           <t>社區議題</t>
         </is>
       </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年下半年度藝文及民俗節慶活動補助</t>
+          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>115年下半年度藝文及民俗節慶活動補助</t>
+          <t>115年文化部社造築夢培養皿徵選獎勵計畫</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年下半年度藝文及民俗節慶活動補助</t>
+          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
+          <t>www.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>www.moc.gov.tw</t>
+        </is>
+      </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-445/</t>
+          <t>https://dayseechat.com/subsidy/grant-387/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>基隆市青年參與公益活動補助計畫</t>
+          <t>115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>數位發展部</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>學校｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>基隆</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
+          <t>創新創業｜產業發展</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
+          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>基隆市青年參與公益活動補助計畫</t>
+          <t>115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
+          <t>https://moda.gov.tw/</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>dsa.dyhu.edu.tw</t>
+          <t>moda.gov.tw</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
+          <t>https://moda.gov.tw/</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>dsa.dyhu.edu.tw</t>
+          <t>moda.gov.tw</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-389/</t>
+          <t>https://dayseechat.com/subsidy/grant-429/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>數位發展部</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>企業｜學校｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3391,83 +4200,87 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬｜51萬-100萬</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>高齡</t>
+          <t>創新創業｜產業發展</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>高齡</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
+          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
+          <t>https://moda.gov.tw/</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>wlb.mol.gov.tw</t>
+          <t>moda.gov.tw</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
+          <t>https://moda.gov.tw/</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>wlb.mol.gov.tw</t>
+          <t>moda.gov.tw</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-368/</t>
+          <t>https://dayseechat.com/subsidy/grant-448/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115學年度精進童軍教育發展實施計畫</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>教育部</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>企業｜學校｜民間團體</t>
+          <t>學校</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3477,27 +4290,27 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜社區議題</t>
+          <t>孩童｜青年</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>孩童</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>青年</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -3505,32 +4318,32 @@
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.google.com/search?q=115學年度精進童軍教育發展實施計畫</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115學年度精進童軍教育發展實施計畫</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>https://www.mol.gov.tw/</t>
+          <t>https://www.edu.tw/</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>www.mol.gov.tw</t>
+          <t>www.edu.tw</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>https://www.mol.gov.tw/</t>
+          <t>https://www.edu.tw/</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>www.mol.gov.tw</t>
+          <t>www.edu.tw</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -3540,54 +4353,54 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-409/</t>
+          <t>https://dayseechat.com/subsidy/grant-444/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>115年度經濟部中小企業創新研發AI轉型補助計畫</t>
+          <t>115年下半年度藝文及民俗節慶活動補助</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>創新創業｜產業發展</t>
+          <t>文化藝文｜社區議題</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>創新創業</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -3595,49 +4408,41 @@
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度經濟部中小企業創新研發AI轉型補助計畫</t>
+          <t>https://www.google.com/search?q=115年下半年度藝文及民俗節慶活動補助</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>115年度經濟部中小企業創新研發AI轉型補助計畫</t>
+          <t>115年下半年度藝文及民俗節慶活動補助</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>https://www.moea.gov.tw/</t>
+          <t>https://www.google.com/search?q=115年下半年度藝文及民俗節慶活動補助</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>www.moea.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.moea.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>www.moea.gov.tw</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-395/</t>
+          <t>https://dayseechat.com/subsidy/grant-445/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫</t>
+          <t>基隆市青年參與公益活動補助計畫</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3647,12 +4452,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>桃園</t>
+          <t>基隆</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3662,17 +4467,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>青年</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>青年</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -3681,59 +4486,59 @@
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
+          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫</t>
+          <t>基隆市青年參與公益活動補助計畫</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
+          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>tyoem.tycg.gov.tw</t>
+          <t>dsa.dyhu.edu.tw</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
+          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>tyoem.tycg.gov.tw</t>
+          <t>dsa.dyhu.edu.tw</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-351/</t>
+          <t>https://dayseechat.com/subsidy/grant-389/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>115年文化部青年村落文化行動計畫</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>個人｜民間團體</t>
+          <t>企業｜學校｜民間團體</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3743,22 +4548,22 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>高齡</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>高齡</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -3767,59 +4572,59 @@
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年文化部青年村落文化行動計畫</t>
+          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>115年文化部青年村落文化行動計畫</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/</t>
+          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>www.moc.gov.tw</t>
+          <t>wlb.mol.gov.tw</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/</t>
+          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>www.moc.gov.tw</t>
+          <t>wlb.mol.gov.tw</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-394/</t>
+          <t>https://dayseechat.com/subsidy/grant-368/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>客家影像畢業製作孵育計畫徵選</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>客家委員會</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>學校</t>
+          <t>企業｜學校｜民間團體</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3829,27 +4634,27 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬｜51萬-100萬</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>客家｜文化藝文</t>
+          <t>產業發展｜社區議題</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>客家</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -3857,59 +4662,59 @@
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>客家影像畢業製作孵育計畫徵選</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>www.hakka.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>www.hakka.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-294/</t>
+          <t>https://dayseechat.com/subsidy/grant-409/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>115年度不孕症試管嬰兒補助3.0方案</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>衛生福利部</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>個人</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3919,56 +4724,60 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>100萬以上｜10萬以下｜11萬-50萬｜51萬-100萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>孩童</t>
+          <t>婦女｜產業發展</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>孩童</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度不孕症試管嬰兒補助3.0方案</t>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>115年度不孕症試管嬰兒補助3.0方案</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>https://www.mohw.gov.tw/</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>www.mohw.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>https://www.mohw.gov.tw/</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>www.mohw.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -3978,115 +4787,123 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-401/</t>
+          <t>https://dayseechat.com/subsidy/grant-438/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>115年度台中市都市更新整建維護補助計畫</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>台中</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>婦女｜產業發展｜青年</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>https://www.taichung.gov.tw/3234351/post</t>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>115年度台中市都市更新整建維護補助計畫</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>https://www.taichung.gov.tw/3234351/post</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>www.taichung.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>https://www.taichung.gov.tw/3234351/post</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>www.taichung.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-369/</t>
+          <t>https://dayseechat.com/subsidy/grant-446/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>115年度台中拍獎勵電影事業計畫</t>
+          <t>115年度經濟部中小企業創新研發AI轉型補助計畫</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>經濟部</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>企業｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>台中</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4096,17 +4913,17 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>文化藝文｜產業發展</t>
+          <t>創新創業｜產業發展</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>創新創業</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -4119,41 +4936,49 @@
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度台中拍獎勵電影事業計畫</t>
+          <t>https://www.google.com/search?q=115年度經濟部中小企業創新研發AI轉型補助計畫</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>115年度台中拍獎勵電影事業計畫</t>
+          <t>115年度經濟部中小企業創新研發AI轉型補助計畫</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度台中拍獎勵電影事業計畫</t>
+          <t>https://www.moea.gov.tw/</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moea.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>www.moea.gov.tw</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-417/</t>
+          <t>https://dayseechat.com/subsidy/grant-395/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>115年度臺北市住宅社區創能儲能及節能補助計畫</t>
+          <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4163,27 +4988,27 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>個人｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>桃園</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬｜51萬-100萬</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>生態環境｜社區議題</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -4191,42 +5016,38 @@
           <t>生態環境</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
+          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>115年度臺北市住宅社區創能儲能及節能補助計畫</t>
+          <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
+          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>www.gov.taipei</t>
+          <t>tyoem.tycg.gov.tw</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
+          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>www.gov.taipei</t>
+          <t>tyoem.tycg.gov.tw</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -4236,49 +5057,49 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-371/</t>
+          <t>https://dayseechat.com/subsidy/grant-351/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫</t>
+          <t>115年文化部青年村落文化行動計畫</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>個人｜民間團體</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -4287,165 +5108,169 @@
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>https://www.twtainan.net/</t>
+          <t>https://www.google.com/search?q=115年文化部青年村落文化行動計畫</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫</t>
+          <t>115年文化部青年村落文化行動計畫</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>https://www.twtainan.net/</t>
+          <t>https://www.moc.gov.tw/</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>www.twtainan.net</t>
+          <t>www.moc.gov.tw</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>https://www.twtainan.net/</t>
+          <t>https://www.moc.gov.tw/</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>www.twtainan.net</t>
+          <t>www.moc.gov.tw</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-385/</t>
+          <t>https://dayseechat.com/subsidy/grant-394/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026新竹市政府青年AI數位工具補助</t>
+          <t>客家影像畢業製作孵育計畫徵選</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>客家委員會</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>個人</t>
+          <t>學校</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>新竹</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
+          <t>客家｜文化藝文</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+          <t>客家</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2026新竹市政府青年AI數位工具補助</t>
+          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2026新竹市政府青年AI數位工具補助</t>
+          <t>客家影像畢業製作孵育計畫徵選</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>https://youthhsinchu.hccg.gov.tw/</t>
+          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>youthhsinchu.hccg.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>https://youthhsinchu.hccg.gov.tw/</t>
+          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>youthhsinchu.hccg.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>manual_verified_override</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-399/</t>
+          <t>https://dayseechat.com/subsidy/grant-294/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>115年度推動社區發展及互助共好補助計畫</t>
+          <t>115年度不孕症試管嬰兒補助3.0方案</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>衛生福利部</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>100萬以上｜10萬以下｜11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>孩童｜社區議題｜高齡</t>
+          <t>孩童</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -4453,149 +5278,141 @@
           <t>孩童</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>高齡</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動社區發展及互助共好補助計畫</t>
+          <t>https://www.google.com/search?q=115年度不孕症試管嬰兒補助3.0方案</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>115年度推動社區發展及互助共好補助計畫</t>
+          <t>115年度不孕症試管嬰兒補助3.0方案</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動社區發展及互助共好補助計畫</t>
+          <t>https://www.mohw.gov.tw/</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr"/>
+          <t>www.mohw.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mohw.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>www.mohw.gov.tw</t>
+        </is>
+      </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-408/</t>
+          <t>https://dayseechat.com/subsidy/grant-401/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>115年度推動資源循環地方創生計畫</t>
+          <t>115年度台中市都市更新整建維護補助計畫</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>環境部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>企業｜民間團體</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>生態環境｜產業發展｜社區議題</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
           <t>社區議題</t>
         </is>
       </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動資源循環地方創生計畫</t>
+          <t>https://www.taichung.gov.tw/3234351/post</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>115年度推動資源循環地方創生計畫</t>
+          <t>115年度台中市都市更新整建維護補助計畫</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>https://www.moenv.gov.tw/</t>
+          <t>https://www.taichung.gov.tw/3234351/post</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>www.moenv.gov.tw</t>
+          <t>www.taichung.gov.tw</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>https://www.moenv.gov.tw/</t>
+          <t>https://www.taichung.gov.tw/3234351/post</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>www.moenv.gov.tw</t>
+          <t>www.taichung.gov.tw</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-412/</t>
+          <t>https://dayseechat.com/subsidy/grant-369/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
+          <t>115年度台中拍獎勵電影事業計畫</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -4605,37 +5422,37 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>基隆</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>社區議題｜身心障礙</t>
+          <t>文化藝文｜產業發展</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>身心障礙</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -4643,49 +5460,41 @@
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
+          <t>https://www.google.com/search?q=115年度台中拍獎勵電影事業計畫</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
+          <t>115年度台中拍獎勵電影事業計畫</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>https://www.klcg.gov.tw/</t>
+          <t>https://www.google.com/search?q=115年度台中拍獎勵電影事業計畫</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>www.klcg.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.klcg.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>www.klcg.gov.tw</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-433/</t>
+          <t>https://dayseechat.com/subsidy/grant-417/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>高雄市政府會議展覽活動擴大補助計畫</t>
+          <t>115年度臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4695,37 +5504,37 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>企業｜其他對象｜學校｜民間團體</t>
+          <t>個人｜民間團體</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>高雄</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>文化藝文｜產業發展</t>
+          <t>生態環境｜社區議題</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -4733,89 +5542,89 @@
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=高雄市政府會議展覽活動擴大補助計畫</t>
+          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>高雄市政府會議展覽活動擴大補助計畫</t>
+          <t>115年度臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>https://www.kcg.gov.tw/</t>
+          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>www.kcg.gov.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>https://www.kcg.gov.tw/</t>
+          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>www.kcg.gov.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-435/</t>
+          <t>https://dayseechat.com/subsidy/grant-371/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>115年度A+企業創新研發淬錬次世代通訊計畫</t>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>企業｜民間團體</t>
+          <t>個人｜其他對象｜民間團體</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>創新創業｜產業發展</t>
+          <t>生態環境｜社區議題</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>創新創業</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -4823,32 +5632,32 @@
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度A%2B企業創新研發淬錬次世代通訊計畫</t>
+          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>115年度A+企業創新研發淬錬次世代通訊計畫</t>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>https://www.moea.gov.tw/</t>
+          <t>https://www.gov.taipei/</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>www.moea.gov.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>https://www.moea.gov.tw/</t>
+          <t>https://www.gov.taipei/</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>www.moea.gov.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -4858,14 +5667,14 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-442/</t>
+          <t>https://dayseechat.com/subsidy/grant-440/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+          <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4875,12 +5684,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>企業｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>新北</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4890,7 +5699,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -4909,49 +5718,49 @@
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+          <t>https://www.twtainan.net/</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+          <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
+          <t>https://www.twtainan.net/</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>www.economic.ntpc.gov.tw</t>
+          <t>www.twtainan.net</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
+          <t>https://www.twtainan.net/</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>www.economic.ntpc.gov.tw</t>
+          <t>www.twtainan.net</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>manual_verified_override</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-410/</t>
+          <t>https://dayseechat.com/subsidy/grant-385/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+          <t>2026新竹市政府青年AI數位工具補助</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -4961,12 +5770,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>企業｜民間團體</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>新北</t>
+          <t>新竹</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4976,17 +5785,17 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>青年</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>青年</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -4995,32 +5804,32 @@
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+          <t>https://www.google.com/search?q=2026新竹市政府青年AI數位工具補助</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
+          <t>2026新竹市政府青年AI數位工具補助</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
+          <t>https://youthhsinchu.hccg.gov.tw/</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>www.economic.ntpc.gov.tw</t>
+          <t>youthhsinchu.hccg.gov.tw</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
+          <t>https://youthhsinchu.hccg.gov.tw/</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>www.economic.ntpc.gov.tw</t>
+          <t>youthhsinchu.hccg.gov.tw</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
@@ -5030,14 +5839,14 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-420/</t>
+          <t>https://dayseechat.com/subsidy/grant-399/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>115年度新北市低碳社區改造補助</t>
+          <t>115年度推動社區發展及互助共好補助計畫</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -5047,32 +5856,32 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>其他對象</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>新北</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>10萬以下｜11萬-50萬｜51萬-100萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>生態環境｜社區議題</t>
+          <t>孩童｜社區議題｜高齡</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>孩童</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -5080,155 +5889,159 @@
           <t>社區議題</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>高齡</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
+          <t>https://www.google.com/search?q=115年度推動社區發展及互助共好補助計畫</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>115年度新北市低碳社區改造補助</t>
+          <t>115年度推動社區發展及互助共好補助計畫</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
+          <t>https://www.google.com/search?q=115年度推動社區發展及互助共好補助計畫</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>www.epd.ntpc.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>www.epd.ntpc.gov.tw</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-378/</t>
+          <t>https://dayseechat.com/subsidy/grant-408/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>115年度補助文化活動作業</t>
+          <t>115年度推動資源循環地方創生計畫</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>環境部</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>個人｜民間團體</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>基隆</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>生態環境｜產業發展｜社區議題</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
+          <t>https://www.google.com/search?q=115年度推動資源循環地方創生計畫</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>115年度補助文化活動作業</t>
+          <t>115年度推動資源循環地方創生計畫</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
+          <t>https://www.moenv.gov.tw/</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>klctb.klcg.gov.tw</t>
+          <t>www.moenv.gov.tw</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
+          <t>https://www.moenv.gov.tw/</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>klctb.klcg.gov.tw</t>
+          <t>www.moenv.gov.tw</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-314/</t>
+          <t>https://dayseechat.com/subsidy/grant-412/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
+          <t>115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>衛生福利部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>個人</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>基隆</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5238,59 +6051,55 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>婦女｜孩童｜身心障礙</t>
+          <t>社區議題｜身心障礙</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>婦女</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>孩童</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
           <t>身心障礙</t>
         </is>
       </c>
+      <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=%E8%A1%9B%E7%94%9F%E7%A6%8F%E5%88%A9%E9%83%A8%E7%A4%BE%E6%9C%83%E5%8F%8A%E5%AE%B6%E5%BA%AD%E7%BD%B2114%E5%B9%B4%E5%96%AE%E8%A6%AA%E6%89%B6%E5%8A%A9%E8%A8%88%E7%95%AB</t>
+          <t>https://www.google.com/search?q=115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
+          <t>115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>https://www.mohw.gov.tw/</t>
+          <t>https://www.klcg.gov.tw/</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>www.mohw.gov.tw</t>
+          <t>www.klcg.gov.tw</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>https://www.mohw.gov.tw/</t>
+          <t>https://www.klcg.gov.tw/</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>www.mohw.gov.tw</t>
+          <t>www.klcg.gov.tw</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
@@ -5300,14 +6109,14 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-246/</t>
+          <t>https://dayseechat.com/subsidy/grant-433/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>115年臺南地方產業原鄉永續小旅行振興計畫</t>
+          <t>高雄市政府會議展覽活動擴大補助計畫</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -5317,32 +6126,32 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>企業｜其他對象｜學校｜民間團體</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>高雄</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>生態環境｜產業發展</t>
+          <t>文化藝文｜產業發展</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -5355,41 +6164,49 @@
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
+          <t>https://www.google.com/search?q=高雄市政府會議展覽活動擴大補助計畫</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>115年臺南地方產業原鄉永續小旅行振興計畫</t>
+          <t>高雄市政府會議展覽活動擴大補助計畫</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
+          <t>https://www.kcg.gov.tw/</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
+          <t>www.kcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>www.kcg.gov.tw</t>
+        </is>
+      </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-391/</t>
+          <t>https://dayseechat.com/subsidy/grant-435/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>115年度AI工具庫點數補助計畫</t>
+          <t>115年度A+企業創新研發淬錬次世代通訊計畫</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -5399,7 +6216,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -5409,12 +6226,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -5437,12 +6254,12 @@
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度AI工具庫點數補助計畫</t>
+          <t>https://www.google.com/search?q=115年度A%2B企業創新研發淬錬次世代通訊計畫</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>115年度AI工具庫點數補助計畫</t>
+          <t>115年度A+企業創新研發淬錬次世代通訊計畫</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -5472,14 +6289,14 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-430/</t>
+          <t>https://dayseechat.com/subsidy/grant-442/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>115年度台中市公寓大廈成立管委會獎勵補助計畫</t>
+          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -5489,32 +6306,32 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>台中</t>
+          <t>新北</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -5523,49 +6340,49 @@
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
+          <t>https://www.google.com/search?q=115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>115年度台中市公寓大廈成立管委會獎勵補助計畫</t>
+          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
+          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>thd.taichung.gov.tw</t>
+          <t>www.economic.ntpc.gov.tw</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
+          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>thd.taichung.gov.tw</t>
+          <t>www.economic.ntpc.gov.tw</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>manual_verified_override</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-370/</t>
+          <t>https://dayseechat.com/subsidy/grant-410/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>115年度台中市公寓大廈成立管理委員會補助</t>
+          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -5575,12 +6392,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>其他對象｜民間團體</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>台中</t>
+          <t>新北</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5590,17 +6407,17 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -5609,89 +6426,89 @@
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度台中市公寓大廈成立管理委員會補助</t>
+          <t>https://www.google.com/search?q=115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>115年度台中市公寓大廈成立管理委員會補助</t>
+          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>https://www.taichung.gov.tw/</t>
+          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>www.taichung.gov.tw</t>
+          <t>www.economic.ntpc.gov.tw</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>https://www.taichung.gov.tw/</t>
+          <t>https://www.economic.ntpc.gov.tw/Api/News/Page?id=7127</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>www.taichung.gov.tw</t>
+          <t>www.economic.ntpc.gov.tw</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>manual_verified_override</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-390/</t>
+          <t>https://dayseechat.com/subsidy/grant-420/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>115年度推動事業單位辦理職前培訓計畫</t>
+          <t>115年度新北市低碳社區改造補助</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>企業｜學校</t>
+          <t>其他對象</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>台中</t>
+          <t>新北</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>10萬以下｜11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜青年</t>
+          <t>生態環境｜社區議題</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -5699,32 +6516,32 @@
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
+          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>115年度推動事業單位辦理職前培訓計畫</t>
+          <t>115年度新北市低碳社區改造補助</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
+          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>tcnr.wda.gov.tw</t>
+          <t>www.epd.ntpc.gov.tw</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
+          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>tcnr.wda.gov.tw</t>
+          <t>www.epd.ntpc.gov.tw</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
@@ -5734,14 +6551,14 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-334/</t>
+          <t>https://dayseechat.com/subsidy/grant-378/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>115年臺南市民旅遊補助計畫</t>
+          <t>115年度補助文化活動作業</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -5751,12 +6568,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>個人｜民間團體</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>基隆</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5766,17 +6583,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -5785,135 +6602,143 @@
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年臺南市民旅遊補助計畫</t>
+          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>115年臺南市民旅遊補助計畫</t>
+          <t>115年度補助文化活動作業</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>https://www.tainan.gov.tw/</t>
+          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>www.tainan.gov.tw</t>
+          <t>klctb.klcg.gov.tw</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>https://www.tainan.gov.tw/</t>
+          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>www.tainan.gov.tw</t>
+          <t>klctb.klcg.gov.tw</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-392/</t>
+          <t>https://dayseechat.com/subsidy/grant-314/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>115年品牌臺東產業行銷補助</t>
+          <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>衛生福利部</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>企業｜民間團體</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>台東</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>10萬以下｜11萬-50萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>婦女｜孩童｜身心障礙</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>孩童</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>身心障礙</t>
+        </is>
+      </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
+          <t>https://www.google.com/search?q=%E8%A1%9B%E7%94%9F%E7%A6%8F%E5%88%A9%E9%83%A8%E7%A4%BE%E6%9C%83%E5%8F%8A%E5%AE%B6%E5%BA%AD%E7%BD%B2114%E5%B9%B4%E5%96%AE%E8%A6%AA%E6%89%B6%E5%8A%A9%E8%A8%88%E7%95%AB</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>115年品牌臺東產業行銷補助</t>
+          <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
+          <t>https://www.mohw.gov.tw/</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>bdsone.taitung.gov.tw</t>
+          <t>www.mohw.gov.tw</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
+          <t>https://www.mohw.gov.tw/</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>bdsone.taitung.gov.tw</t>
+          <t>www.mohw.gov.tw</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-284/</t>
+          <t>https://dayseechat.com/subsidy/grant-246/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>115年度高雄市觀光行銷推廣補助計畫</t>
+          <t>115年臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -5923,152 +6748,152 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>高雄</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>10萬以下｜11萬-50萬</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>生態環境｜產業發展</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>https://khh.travel/zh-tw/event/news/7268/</t>
+          <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>115年度高雄市觀光行銷推廣補助計畫</t>
+          <t>115年臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>https://khh.travel/zh-tw/event/news/7268/</t>
+          <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>khh.travel</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>https://khh.travel/zh-tw/event/news/7268/</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>khh.travel</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-327/</t>
+          <t>https://dayseechat.com/subsidy/grant-391/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>115年臺南市家戶屋頂設置太陽光電加速計畫</t>
+          <t>115年度AI工具庫點數補助計畫</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>經濟部</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>個人</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>100萬以上｜10萬以下</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>創新創業｜產業發展</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115%E5%B9%B4%E8%87%BA%E5%8D%97%E5%B8%82%E5%AE%B6%E6%88%B6%E5%B1%8B%E9%A0%82%E8%A8%AD%E7%BD%AE%E5%A4%AA%E9%99%BD%E5%85%89%E9%9B%BB%E5%8A%A0%E9%80%9F%E8%A8%88%E7%95%AB</t>
+          <t>https://www.google.com/search?q=115年度AI工具庫點數補助計畫</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>115年臺南市家戶屋頂設置太陽光電加速計畫</t>
+          <t>115年度AI工具庫點數補助計畫</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>https://www.tainan.gov.tw/</t>
+          <t>https://www.moea.gov.tw/</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>www.tainan.gov.tw</t>
+          <t>www.moea.gov.tw</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>https://www.tainan.gov.tw/</t>
+          <t>https://www.moea.gov.tw/</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>www.tainan.gov.tw</t>
+          <t>www.moea.gov.tw</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
@@ -6078,14 +6903,14 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-380/</t>
+          <t>https://dayseechat.com/subsidy/grant-430/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>115年度高雄市公寓大廈共用部分維護修繕費用補助</t>
+          <t>115年度台中市公寓大廈成立管委會獎勵補助計畫</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -6095,32 +6920,32 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>其他對象</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>高雄</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -6129,49 +6954,49 @@
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115%E5%B9%B4%E5%BA%A6%E9%AB%98%E9%9B%84%E5%B8%82%E5%85%AC%E5%AF%93%E5%A4%A7%E5%BB%88%E5%85%B1%E7%94%A8%E9%83%A8%E5%88%86%E7%B6%AD%E8%AD%B7%E4%BF%AE%E7%B9%95%E8%B2%BB%E7%94%A8%E8%A3%9C%E5%8A%A9</t>
+          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>115年度高雄市公寓大廈共用部分維護修繕費用補助</t>
+          <t>115年度台中市公寓大廈成立管委會獎勵補助計畫</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>https://www.kcg.gov.tw/</t>
+          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>www.kcg.gov.tw</t>
+          <t>thd.taichung.gov.tw</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>https://www.kcg.gov.tw/</t>
+          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>www.kcg.gov.tw</t>
+          <t>thd.taichung.gov.tw</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-381/</t>
+          <t>https://dayseechat.com/subsidy/grant-370/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>115年度彰化縣社區發展協會一般性補助</t>
+          <t>115年度台中市公寓大廈成立管理委員會補助</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -6181,22 +7006,22 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>其他對象｜民間團體</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>彰化</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -6215,32 +7040,32 @@
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度彰化縣社區發展協會一般性補助</t>
+          <t>https://www.google.com/search?q=115年度台中市公寓大廈成立管理委員會補助</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>115年度彰化縣社區發展協會一般性補助</t>
+          <t>115年度台中市公寓大廈成立管理委員會補助</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>https://www.chcg.gov.tw/</t>
+          <t>https://www.taichung.gov.tw/</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>www.chcg.gov.tw</t>
+          <t>www.taichung.gov.tw</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>https://www.chcg.gov.tw/</t>
+          <t>https://www.taichung.gov.tw/</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>www.chcg.gov.tw</t>
+          <t>www.taichung.gov.tw</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
@@ -6250,100 +7075,104 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-419/</t>
+          <t>https://dayseechat.com/subsidy/grant-390/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>115年度彰化縣社區發展協會一般性補助</t>
+          <t>115年度推動事業單位辦理職前培訓計畫</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>企業｜學校</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>彰化</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
+          <t>產業發展｜青年</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度彰化縣社區發展協會一般性補助</t>
+          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>115年度彰化縣社區發展協會一般性補助</t>
+          <t>115年度推動事業單位辦理職前培訓計畫</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>https://www.chcg.gov.tw/</t>
+          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>www.chcg.gov.tw</t>
+          <t>tcnr.wda.gov.tw</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>https://www.chcg.gov.tw/</t>
+          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>www.chcg.gov.tw</t>
+          <t>tcnr.wda.gov.tw</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-424/</t>
+          <t>https://dayseechat.com/subsidy/grant-334/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
+          <t>115年臺南市民旅遊補助計畫</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -6358,7 +7187,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>基隆</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -6368,55 +7197,51 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>生態環境｜產業發展</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
           <t>產業發展</t>
         </is>
       </c>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
+          <t>https://www.google.com/search?q=115年臺南市民旅遊補助計畫</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
+          <t>115年臺南市民旅遊補助計畫</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>https://www.klcg.gov.tw/</t>
+          <t>https://www.tainan.gov.tw/</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>www.klcg.gov.tw</t>
+          <t>www.tainan.gov.tw</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>https://www.klcg.gov.tw/</t>
+          <t>https://www.tainan.gov.tw/</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>www.klcg.gov.tw</t>
+          <t>www.tainan.gov.tw</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
@@ -6426,14 +7251,14 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-415/</t>
+          <t>https://dayseechat.com/subsidy/grant-392/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>全國性運動團體辦理全民運動相關活動計畫</t>
+          <t>115年品牌臺東產業行銷補助</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -6443,32 +7268,32 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台東</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -6477,32 +7302,32 @@
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>全國性運動團體辦理全民運動相關活動計畫</t>
+          <t>115年品牌臺東產業行銷補助</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>isports.sa.gov.tw</t>
+          <t>bdsone.taitung.gov.tw</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>isports.sa.gov.tw</t>
+          <t>bdsone.taitung.gov.tw</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
@@ -6512,49 +7337,49 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-300/</t>
+          <t>https://dayseechat.com/subsidy/grant-284/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>115年度小型企業創新研發計畫SBIR</t>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -6563,49 +7388,41 @@
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>https://sbir.org.tw/</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>115年度小型企業創新研發計畫SBIR</t>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://sbir.org.tw/</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>sbir.org.tw</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>https://sbir.org.tw/</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>sbir.org.tw</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-365/</t>
+          <t>https://dayseechat.com/subsidy/grant-441/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>115年度臺北市產業發展獎勵補助計畫SITI</t>
+          <t>115年度高雄市觀光行銷推廣補助計畫</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -6615,22 +7432,22 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>高雄</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -6649,32 +7466,32 @@
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>https://www.industry-incentive.taipei/</t>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>115年度臺北市產業發展獎勵補助計畫SITI</t>
+          <t>115年度高雄市觀光行銷推廣補助計畫</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>https://www.industry-incentive.taipei/</t>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>www.industry-incentive.taipei</t>
+          <t>khh.travel</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>https://www.industry-incentive.taipei/</t>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>www.industry-incentive.taipei</t>
+          <t>khh.travel</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
@@ -6684,49 +7501,49 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-363/</t>
+          <t>https://dayseechat.com/subsidy/grant-327/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>115年海洋保育國際交流活動獎助計畫</t>
+          <t>115年臺南市家戶屋頂設置太陽光電加速計畫</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>海洋委員會</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>個人｜學校｜民間團體</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>10萬以下｜11萬-50萬</t>
+          <t>100萬以上｜10萬以下</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -6735,49 +7552,49 @@
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+          <t>https://www.google.com/search?q=115%E5%B9%B4%E8%87%BA%E5%8D%97%E5%B8%82%E5%AE%B6%E6%88%B6%E5%B1%8B%E9%A0%82%E8%A8%AD%E7%BD%AE%E5%A4%AA%E9%99%BD%E5%85%89%E9%9B%BB%E5%8A%A0%E9%80%9F%E8%A8%88%E7%95%AB</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>115年海洋保育國際交流活動獎助計畫</t>
+          <t>115年臺南市家戶屋頂設置太陽光電加速計畫</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+          <t>https://www.tainan.gov.tw/</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>www.oca.gov.tw</t>
+          <t>www.tainan.gov.tw</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+          <t>https://www.tainan.gov.tw/</t>
         </is>
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>www.oca.gov.tw</t>
+          <t>www.tainan.gov.tw</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-319/</t>
+          <t>https://dayseechat.com/subsidy/grant-380/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
+          <t>115年度高雄市公寓大廈共用部分維護修繕費用補助</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -6787,12 +7604,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>其他對象</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>新北</t>
+          <t>高雄</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6802,107 +7619,103 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>孩童｜社區議題</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>孩童</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
+          <t>https://www.google.com/search?q=115%E5%B9%B4%E5%BA%A6%E9%AB%98%E9%9B%84%E5%B8%82%E5%85%AC%E5%AF%93%E5%A4%A7%E5%BB%88%E5%85%B1%E7%94%A8%E9%83%A8%E5%88%86%E7%B6%AD%E8%AD%B7%E4%BF%AE%E7%B9%95%E8%B2%BB%E7%94%A8%E8%A3%9C%E5%8A%A9</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
+          <t>115年度高雄市公寓大廈共用部分維護修繕費用補助</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>https://www.sw.ntpc.gov.tw/</t>
+          <t>https://www.kcg.gov.tw/</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>www.sw.ntpc.gov.tw</t>
+          <t>www.kcg.gov.tw</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>https://www.sw.ntpc.gov.tw/</t>
+          <t>https://www.kcg.gov.tw/</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>www.sw.ntpc.gov.tw</t>
+          <t>www.kcg.gov.tw</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>manual_verified_override</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-428/</t>
+          <t>https://dayseechat.com/subsidy/grant-381/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>商業服務業AI解決方案補助計畫</t>
+          <t>115年度彰化縣社區發展協會一般性補助</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>彰化</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -6911,49 +7724,49 @@
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+          <t>https://www.google.com/search?q=115年度彰化縣社區發展協會一般性補助</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>商業服務業AI解決方案補助計畫</t>
+          <t>115年度彰化縣社區發展協會一般性補助</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+          <t>https://www.chcg.gov.tw/</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>www.smebiz.org.tw</t>
+          <t>www.chcg.gov.tw</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+          <t>https://www.chcg.gov.tw/</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>www.smebiz.org.tw</t>
+          <t>www.chcg.gov.tw</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-359/</t>
+          <t>https://dayseechat.com/subsidy/grant-419/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫</t>
+          <t>115年度彰化縣社區發展協會一般性補助</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -6968,22 +7781,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>基隆</t>
+          <t>彰化</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>100萬以上｜10萬以下</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>社區議題｜高齡</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6991,59 +7804,55 @@
           <t>社區議題</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>高齡</t>
-        </is>
-      </c>
+      <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+          <t>https://www.google.com/search?q=115年度彰化縣社區發展協會一般性補助</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫</t>
+          <t>115年度彰化縣社區發展協會一般性補助</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+          <t>https://www.chcg.gov.tw/</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>www.klcg.gov.tw</t>
+          <t>www.chcg.gov.tw</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+          <t>https://www.chcg.gov.tw/</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>www.klcg.gov.tw</t>
+          <t>www.chcg.gov.tw</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-331/</t>
+          <t>https://dayseechat.com/subsidy/grant-424/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2026-2027高雄馬祖團體旅遊補助計畫</t>
+          <t>115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -7058,7 +7867,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>連江｜高雄</t>
+          <t>基隆</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -7068,70 +7877,82 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
+          <t>生態環境｜產業發展</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
+          <t>https://www.google.com/search?q=115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>2026高雄馬祖團體旅遊補助計畫</t>
+          <t>115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
+          <t>https://www.klcg.gov.tw/</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q75" s="2" t="inlineStr"/>
-      <c r="R75" s="2" t="inlineStr"/>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-383/</t>
+          <t>https://dayseechat.com/subsidy/grant-415/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>商業服務業AI解決方案補助計畫</t>
+          <t>全國性運動團體辦理全民運動相關活動計畫</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -7141,22 +7962,22 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2027-10-20</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -7165,396 +7986,730 @@
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
+          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>全國性運動團體辦理全民運動相關活動計畫</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>isports.sa.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>isports.sa.gov.tw</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-300/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>115年度小型企業創新研發計畫SBIR</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>https://sbir.org.tw/</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>115年度小型企業創新研發計畫SBIR</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>https://sbir.org.tw/</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>sbir.org.tw</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>https://sbir.org.tw/</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>sbir.org.tw</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-365/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>115年度臺北市產業發展獎勵補助計畫SITI</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.industry-incentive.taipei/</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>115年度臺北市產業發展獎勵補助計畫SITI</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.industry-incentive.taipei/</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>www.industry-incentive.taipei</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.industry-incentive.taipei/</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>www.industry-incentive.taipei</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-363/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>115年海洋保育國際交流活動獎助計畫</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>海洋委員會</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>個人｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下｜11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>115年海洋保育國際交流活動獎助計畫</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>www.oca.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>www.oca.gov.tw</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-319/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>孩童｜社區議題</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>孩童</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sw.ntpc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>www.sw.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sw.ntpc.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>www.sw.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>manual_verified_override</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-428/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>商業服務業AI解決方案補助計畫</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
           <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
         </is>
       </c>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr">
         <is>
           <t>商業服務業AI解決方案補助計畫</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr">
+      <c r="P81" s="2" t="inlineStr">
         <is>
           <t>www.smebiz.org.tw</t>
         </is>
       </c>
-      <c r="Q76" s="2" t="inlineStr">
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
         </is>
       </c>
-      <c r="R76" s="2" t="inlineStr">
+      <c r="R81" s="2" t="inlineStr">
         <is>
           <t>www.smebiz.org.tw</t>
         </is>
       </c>
-      <c r="S76" s="2" t="inlineStr">
+      <c r="S81" s="2" t="inlineStr">
         <is>
           <t>direct_non_google</t>
         </is>
       </c>
-      <c r="T76" s="2" t="inlineStr">
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>基隆</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上｜10萬以下</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>社區議題｜高齡</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>高齡</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-331/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-2027高雄馬祖團體旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>連江｜高雄</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>2026高雄馬祖團體旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>bing_title_no_match</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-383/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>商業服務業AI解決方案補助計畫</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2027-10-20</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>商業服務業AI解決方案補助計畫</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>www.smebiz.org.tw</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>www.smebiz.org.tw</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-349/</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="45" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="43" customWidth="1" min="20" max="20"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>plan_source</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>eligible_targets</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>applicable_region</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>grant_amount</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>deadline_date</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>deadline_text</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>topic_1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>topic_2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>topic_3</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>topic_4</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>topic_5</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_site_url_raw</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_search_query</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_site_url</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_site_domain</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>official_organizer_site_url</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>official_organizer_domain</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>official_url_status</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>detail_url</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>bing_title_no_match</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-441/</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>plan_source</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>eligible_targets</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>applicable_region</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>grant_amount</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>deadline_date</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>deadline_text</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>topic_1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>topic_2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>topic_3</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>topic_4</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>topic_5</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_site_url_raw</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_search_query</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_site_url</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_site_domain</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>official_organizer_site_url</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>official_organizer_domain</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>official_url_status</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>detail_url</t>
         </is>
       </c>
     </row>

--- a/state/daysee_grants_delta_latest.xlsx
+++ b/state/daysee_grants_delta_latest.xlsx
@@ -473,7 +473,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -622,11 +622,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -638,7 +638,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="43" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
     <col width="29" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
@@ -740,6 +740,71 @@
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>official_url_confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>115年度高雄市觀光行銷推廣補助計畫</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-327/</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-327/</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>dayseechat.com</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>search_no_match</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
         </is>
       </c>
     </row>

--- a/state/daysee_grants_delta_latest.xlsx
+++ b/state/daysee_grants_delta_latest.xlsx
@@ -464,7 +464,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>83</v>
@@ -476,7 +476,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -630,7 +630,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -764,10 +764,14 @@
           <t>民間團體</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>高雄</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -787,24 +791,24 @@
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-327/</t>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>dayseechat.com</t>
+          <t>khh.travel</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>search_no_match</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -819,11 +823,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -835,9 +839,9 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
-    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="48" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -940,6 +944,221 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-407/</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>search_no_match</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>中小企業接班轉型計畫</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-353/</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.value-chain.com.tw/news_info.asp?id=731</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>www.value-chain.com.tw</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>中小製造業接班傳承AI應用數位轉型主題式研發計畫補助</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-356/</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>keid.nat.gov.tw</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>keid.nat.gov.tw</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
